--- a/gantt_data.xlsx
+++ b/gantt_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I267"/>
+  <dimension ref="A1:I266"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -533,7 +533,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>ויינברג ליזי</t>
+          <t>אברהם ירדן</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -580,7 +580,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>צוויקל נועה</t>
+          <t>ויינברג ליזי</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -627,7 +627,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>הלמן עמית</t>
+          <t>צוויקל נועה</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>פליק נועה</t>
+          <t>מנצור חנה</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -721,7 +721,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>שיילו בר</t>
+          <t>בר שיילו</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -768,7 +768,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>אברהם ירדן</t>
+          <t>אוחנה חן</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -854,7 +854,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>נתן יובל</t>
+          <t>הלמן עמית</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>אוחנה חן</t>
+          <t>דמארי נועה</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>דמארי נועה</t>
+          <t>פליק נועה</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>זוארץ שיראל</t>
+          <t>דולד הדר</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>חן הדר</t>
+          <t>ורנר אליאן</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1183,7 +1183,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>סעדיה שחף</t>
+          <t>זוארץ שיראל</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1210,49 +1210,41 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>LY1</t>
+          <t>LY27</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>JFK</t>
+          <t>EWR</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>ראש צוות</t>
+          <t>טרייני ר״צ</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>ראש צוות</t>
+          <t>טרייני רצ</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>חן נועם</t>
+          <t>נימרק טליה</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>23:45</t>
+          <t>23:15</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>01:00</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>D9</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>שובץ כי העובד מוסמך לתפקיד, פנוי בזמן המשימה וללא חפיפה</t>
-        </is>
-      </c>
+          <t>00:30</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1267,22 +1259,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>דייל 1</t>
+          <t>ראש צוות</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>דייל</t>
+          <t>ראש צוות</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>דולד הדר</t>
+          <t>חן נועם</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>23:55</t>
+          <t>23:45</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1314,7 +1306,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>דייל 2</t>
+          <t>דייל 1</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1324,7 +1316,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>ורנר אליאן</t>
+          <t>חן הדר</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1361,7 +1353,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>דייל 3</t>
+          <t>דייל 2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1408,7 +1400,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>דייל 4</t>
+          <t>דייל 3</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1455,22 +1447,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>מתאם תורים</t>
+          <t>דייל 4</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>מתאם תורים</t>
+          <t>דייל</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>רוב נועה</t>
+          <t>סעדיה שחף</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>23:45</t>
+          <t>23:55</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1502,22 +1494,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>מפקח TSA</t>
+          <t>מתאם תורים</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>מפקח TSA</t>
+          <t>מתאם תורים</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>אהרן נעמה</t>
+          <t>רוב נועה</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>23:45</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1549,17 +1541,17 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>שומר TSA</t>
+          <t>מפקח TSA</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>שומר TSA</t>
+          <t>מפקח TSA</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>לוי ללי לוטם</t>
+          <t>אהרן נעמה</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1586,42 +1578,42 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>LY5</t>
+          <t>LY1</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>LAX</t>
+          <t>JFK</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>ראש צוות</t>
+          <t>שומר TSA</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>ראש צוות</t>
+          <t>שומר TSA</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>סלם חיה</t>
+          <t>אלטלף אגם</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>23:50</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>01:05</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>D8</t>
+          <t>D9</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -1643,22 +1635,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>דייל 1</t>
+          <t>ראש צוות</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>דייל</t>
+          <t>ראש צוות</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>הלמן עמית</t>
+          <t>נתן יובל</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>23:50</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1690,7 +1682,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>דייל 2</t>
+          <t>דייל 1</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1700,7 +1692,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>ויינברג ליזי</t>
+          <t>אברהם ירדן</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1737,7 +1729,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>דייל 3</t>
+          <t>דייל 2</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1747,7 +1739,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>פליק נועה</t>
+          <t>ויינברג ליזי</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1784,7 +1776,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>דייל 4</t>
+          <t>דייל 3</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1831,22 +1823,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>מפקח TSA</t>
+          <t>דייל 4</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>מפקח TSA</t>
+          <t>דייל</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>בן עמי רוני</t>
+          <t>אוחנה חן</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>23:05</t>
+          <t>00:00</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -1878,17 +1870,17 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>שומר TSA</t>
+          <t>מפקח TSA</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>שומר TSA</t>
+          <t>מפקח TSA</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>אלטלף אגם</t>
+          <t>אהרן נעמה</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1925,22 +1917,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>טרייני ר״צ</t>
+          <t>שומר TSA</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>טרייני רצ</t>
+          <t>שומר TSA</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>נימרק טליה</t>
+          <t>אקסלרוד מעיין</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>23:50</t>
+          <t>23:05</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -1948,8 +1940,16 @@
           <t>01:05</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>D8</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>שובץ כי העובד מוסמך לתפקיד, פנוי בזמן המשימה וללא חפיפה</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1974,7 +1974,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>נתן יובל</t>
+          <t>בן דב אורנה</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -2021,7 +2021,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>סלם חיה</t>
+          <t>אלגבסי ג'ולי</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -2068,7 +2068,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>חן נועם</t>
+          <t>בונטונג מאי</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -2095,49 +2095,41 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>LY311</t>
+          <t>LY5501</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>LTN</t>
+          <t>WAW</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>ראש צוות</t>
+          <t>טרייני ר״צ</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>ראש צוות</t>
+          <t>טרייני רצ</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>נטע ונטוררו</t>
+          <t>חוזה רון</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>03:40</t>
+          <t>03:00</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>04:50</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>D1A</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>שובץ כי העובד מוסמך לתפקיד, פנוי בזמן המשימה וללא חפיפה</t>
-        </is>
-      </c>
+          <t>04:00</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2152,22 +2144,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>דייל 1</t>
+          <t>ראש צוות</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>דייל</t>
+          <t>ראש צוות</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>אלטלף אגם</t>
+          <t>ונטוררו נטע</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>03:50</t>
+          <t>03:40</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -2199,7 +2191,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>דייל 2</t>
+          <t>דייל 1</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2209,7 +2201,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>בן עמי רוני</t>
+          <t>מילס איב</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -2246,22 +2238,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>טרייני ר״צ</t>
+          <t>דייל 2</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>טרייני רצ</t>
+          <t>דייל</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>שיר סינדני</t>
+          <t>אלימלך נועה</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>03:40</t>
+          <t>03:50</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -2269,55 +2261,55 @@
           <t>04:50</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr"/>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>D1A</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>שובץ כי העובד מוסמך לתפקיד, פנוי בזמן המשימה וללא חפיפה</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>LY117</t>
+          <t>LY311</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>LTN</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>ראש צוות</t>
+          <t>טרייני ר״צ</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>ראש צוות</t>
+          <t>טרייני רצ</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>נועה אלימלך</t>
+          <t>סינדני שיר</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>03:45</t>
+          <t>03:40</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>05:00</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>D9</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>שובץ כי העובד מוסמך לתפקיד, פנוי בזמן המשימה וללא חפיפה</t>
-        </is>
-      </c>
+          <t>04:50</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2332,22 +2324,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>דייל 1</t>
+          <t>ראש צוות</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>דייל</t>
+          <t>ראש צוות</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>בראל תהילה</t>
+          <t>יהל ענבר</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>03:55</t>
+          <t>03:45</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -2379,7 +2371,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>דייל 2</t>
+          <t>דייל 1</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -2389,7 +2381,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>טטרואשוילי טליה</t>
+          <t>ליטמן עידן</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -2426,7 +2418,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>דייל 3</t>
+          <t>דייל 2</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -2436,7 +2428,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>נוב שני</t>
+          <t>מזרחי עדן</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -2473,7 +2465,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>דייל 4</t>
+          <t>דייל 3</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -2483,7 +2475,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>מזרחי עדן</t>
+          <t>נועה אלימלך</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2520,22 +2512,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>מפקח TSA</t>
+          <t>דייל 4</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>מפקח TSA</t>
+          <t>דייל</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>דן קנה</t>
+          <t>עללוש שחר</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>03:00</t>
+          <t>03:55</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -2567,17 +2559,17 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>שומר TSA</t>
+          <t>מפקח TSA</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>שומר TSA</t>
+          <t>מפקח TSA</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>בן דב אורנה</t>
+          <t>דן קנה</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2614,22 +2606,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>טרייני ר״צ</t>
+          <t>שומר TSA</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>טרייני רצ</t>
+          <t>שומר TSA</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>סינדני שיר</t>
+          <t>ביבי שרון</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>03:45</t>
+          <t>03:00</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -2637,8 +2629,16 @@
           <t>05:00</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr"/>
-      <c r="I48" t="inlineStr"/>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>D9</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>שובץ כי העובד מוסמך לתפקיד, פנוי בזמן המשימה וללא חפיפה</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2710,7 +2710,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>אלימלך נועה</t>
+          <t>שהרבני אוהד</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2757,7 +2757,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>ליטמן עידן</t>
+          <t>אבריאנוב אירינה</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2804,7 +2804,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>אלגבסי ג'ולי</t>
+          <t>טולסטיך חנה</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2843,7 +2843,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>שהרבני אוהד</t>
+          <t>סוקג'אי ג'סמין</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2890,7 +2890,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>סלם חיה</t>
+          <t>אלגבסי ג'ולי</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2937,7 +2937,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>יהל ענבר</t>
+          <t>בונטונג מאי</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2984,7 +2984,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>עללוש שחר</t>
+          <t>בן דב אורנה</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -3031,7 +3031,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>כהן עדי</t>
+          <t>חוזה רון</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>קומרוב דריה</t>
+          <t>בראל תהילה</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -3125,7 +3125,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>חוזה רון</t>
+          <t>לילוב רומי</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -3164,7 +3164,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>חזות דניאל</t>
+          <t>סלם חיה</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -3211,7 +3211,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>רז טל</t>
+          <t>גלאם שני</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -3238,49 +3238,41 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>LY5107</t>
+          <t>LY321</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>TBS</t>
+          <t>MRS</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>ראש צוות</t>
+          <t>טרייני ר״צ</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>ראש צוות</t>
+          <t>טרייני רצ</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>אהרן נעמה</t>
+          <t>שורץ נויה</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>04:30</t>
+          <t>04:25</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>05:30</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>D7</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>שובץ כי העובד מוסמך לתפקיד, פנוי בזמן המשימה וללא חפיפה</t>
-        </is>
-      </c>
+          <t>05:25</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr"/>
+      <c r="I62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -3295,22 +3287,22 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>דייל 1</t>
+          <t>ראש צוות</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>דייל</t>
+          <t>ראש צוות</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>תכלת סגל</t>
+          <t>חזות דניאל</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>04:40</t>
+          <t>04:30</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -3342,7 +3334,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>דייל 2</t>
+          <t>דייל 1</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -3352,7 +3344,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>חן אהב</t>
+          <t>גנץ עטרה</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -3389,22 +3381,22 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>טרייני ר״צ</t>
+          <t>דייל 2</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>טרייני רצ</t>
+          <t>דייל</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>שורץ נויה</t>
+          <t>דז'אנשוילי לינוי</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>04:30</t>
+          <t>04:40</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -3412,8 +3404,16 @@
           <t>05:30</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr"/>
-      <c r="I65" t="inlineStr"/>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>D7</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>שובץ כי העובד מוסמך לתפקיד, פנוי בזמן המשימה וללא חפיפה</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -3438,7 +3438,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>עידן ליטמן</t>
+          <t>רוט גיא</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -3458,7 +3458,7 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>לא נמצא עובד מתאים: אין זמינות, יש חפיפה או שחסרה הסמכה</t>
+          <t>שובץ כי העובד מוסמך לתפקיד, פנוי בזמן המשימה וללא חפיפה</t>
         </is>
       </c>
     </row>
@@ -3485,7 +3485,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>שרעבי רותם</t>
+          <t>חן אהב</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -3532,7 +3532,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>דז'אנשוילי לינוי</t>
+          <t>טטרואשוילי טליה</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -3579,7 +3579,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>שחר עללוש</t>
+          <t>אהרן נעמה</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>לא נמצא עובד מתאים: אין זמינות, יש חפיפה או שחסרה הסמכה</t>
+          <t>שובץ כי העובד מוסמך לתפקיד, פנוי בזמן המשימה וללא חפיפה</t>
         </is>
       </c>
     </row>
@@ -3673,7 +3673,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>מוזס אדיר</t>
+          <t>טרדווי קלייר</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -3720,7 +3720,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>מלטר שנהב</t>
+          <t>ישראל מאיה</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -3747,49 +3747,41 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>LY393</t>
+          <t>LY319</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>BCN</t>
+          <t>CDG</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>ראש צוות</t>
+          <t>טרייני ר״צ</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>ראש צוות</t>
+          <t>טרייני רצ</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>שחר פרגסליך</t>
+          <t>חביב רותם</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>04:45</t>
+          <t>04:40</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>05:45</t>
-        </is>
-      </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>E3</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>לא נמצא עובד מתאים: אין זמינות, יש חפיפה או שחסרה הסמכה</t>
-        </is>
-      </c>
+          <t>05:40</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr"/>
+      <c r="I73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -3804,22 +3796,22 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>דייל 1</t>
+          <t>ראש צוות</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>דייל</t>
+          <t>ראש צוות</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>בן עמי רוני</t>
+          <t>פרגסליך שחר</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>04:55</t>
+          <t>04:45</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -3834,7 +3826,7 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>שובץ כי העובד מוסמך לתפקיד, פנוי בזמן המשימה וללא חפיפה</t>
+          <t>לא נמצא עובד מתאים: אין זמינות, יש חפיפה או שחסרה הסמכה</t>
         </is>
       </c>
     </row>
@@ -3851,7 +3843,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>דייל 2</t>
+          <t>דייל 1</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -3861,7 +3853,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>אלטלף אגם</t>
+          <t>מילס איב</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3898,22 +3890,22 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>מתאם תורים</t>
+          <t>דייל 2</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>מתאם תורים</t>
+          <t>דייל</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>פרילינג דור</t>
+          <t>מלטר שנהב</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>04:45</t>
+          <t>04:55</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -3935,47 +3927,47 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>LY353</t>
+          <t>LY393</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>MUC</t>
+          <t>BCN</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>ראש צוות</t>
+          <t>מתאם תורים</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>ראש צוות</t>
+          <t>מתאם תורים</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>סוקג'אי ג'סמין</t>
+          <t>כהן עדי</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>05:00</t>
+          <t>04:45</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>05:45</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>E5</t>
+          <t>E3</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>לא נמצא עובד מתאים: אין זמינות, יש חפיפה או שחסרה הסמכה</t>
+          <t>שובץ כי העובד מוסמך לתפקיד, פנוי בזמן המשימה וללא חפיפה</t>
         </is>
       </c>
     </row>
@@ -3992,22 +3984,22 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>דייל 1</t>
+          <t>ראש צוות</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>דייל</t>
+          <t>ראש צוות</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>נוב שני</t>
+          <t>אלימלך נועה</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>05:10</t>
+          <t>05:00</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -4039,7 +4031,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>דייל 2</t>
+          <t>דייל 1</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -4049,7 +4041,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>מילס איב</t>
+          <t>אלגבסי ג'ולי</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -4076,32 +4068,32 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>LY5101</t>
+          <t>LY353</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>WAW</t>
+          <t>MUC</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>ראש צוות</t>
+          <t>דייל 2</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>ראש צוות</t>
+          <t>דייל</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>רוט גיא</t>
+          <t>בונטונג מאי</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>05:00</t>
+          <t>05:10</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -4111,44 +4103,44 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>C9</t>
+          <t>E5</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>לא נמצא עובד מתאים: אין זמינות, יש חפיפה או שחסרה הסמכה</t>
+          <t>שובץ כי העובד מוסמך לתפקיד, פנוי בזמן המשימה וללא חפיפה</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>LY5101</t>
+          <t>LY353</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>WAW</t>
+          <t>MUC</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>דייל 1</t>
+          <t>טרייני ר״צ</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>דייל</t>
+          <t>טרייני רצ</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>עידן ליטמן</t>
+          <t>סינדני שיר</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>05:10</t>
+          <t>05:00</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -4156,16 +4148,8 @@
           <t>06:00</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>C9</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>שובץ כי העובד מוסמך לתפקיד, פנוי בזמן המשימה וללא חפיפה</t>
-        </is>
-      </c>
+      <c r="H81" t="inlineStr"/>
+      <c r="I81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -4180,22 +4164,22 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>דייל 2</t>
+          <t>ראש צוות</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>דייל</t>
+          <t>ראש צוות</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>שחר עללוש</t>
+          <t>ונטוררו נטע</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>05:10</t>
+          <t>05:00</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -4210,49 +4194,49 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>שובץ כי העובד מוסמך לתפקיד, פנוי בזמן המשימה וללא חפיפה</t>
+          <t>לא נמצא עובד מתאים: אין זמינות, יש חפיפה או שחסרה הסמכה</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>LY357</t>
+          <t>LY5101</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>WAW</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>ראש צוות</t>
+          <t>דייל 1</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>ראש צוות</t>
+          <t>דייל</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>שחר פרגסליך</t>
+          <t>מוזס אדיר</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>05:05</t>
+          <t>05:10</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>06:05</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>D4</t>
+          <t>C9</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -4264,17 +4248,17 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>LY357</t>
+          <t>LY5101</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>WAW</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>דייל 1</t>
+          <t>דייל 2</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -4284,22 +4268,22 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>מזרחי עדן</t>
+          <t>טולסטיך חנה</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>05:15</t>
+          <t>05:10</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>06:05</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>D4</t>
+          <t>C9</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -4321,22 +4305,22 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>דייל 2</t>
+          <t>ראש צוות</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>דייל</t>
+          <t>ראש צוות</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>רמירז אבריל</t>
+          <t>מזרחי עדן</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>05:15</t>
+          <t>05:05</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -4368,22 +4352,22 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>טרייני ר״צ</t>
+          <t>דייל 1</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>טרייני רצ</t>
+          <t>דייל</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>שיר סינדני</t>
+          <t>מנקר רוני</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>05:05</t>
+          <t>05:15</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -4391,38 +4375,46 @@
           <t>06:05</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr"/>
-      <c r="I86" t="inlineStr"/>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>D4</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>שובץ כי העובד מוסמך לתפקיד, פנוי בזמן המשימה וללא חפיפה</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>LY385</t>
+          <t>LY357</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>FCO</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>ראש צוות</t>
+          <t>דייל 2</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>ראש צוות</t>
+          <t>דייל</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>אלימלך נועה</t>
+          <t>עללוש שחר</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>05:05</t>
+          <t>05:15</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -4432,7 +4424,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>D6</t>
+          <t>D4</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -4454,22 +4446,22 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>דייל 1</t>
+          <t>ראש צוות</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>דייל</t>
+          <t>ראש צוות</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>ליטמן עידן</t>
+          <t>שהרבני אוהד</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>05:15</t>
+          <t>05:05</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -4501,7 +4493,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>דייל 2</t>
+          <t>דייל 1</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -4511,7 +4503,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>שהרבני אוהד</t>
+          <t>רמירז אבריל</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -4548,22 +4540,22 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>טרייני ר״צ</t>
+          <t>דייל 2</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>טרייני רצ</t>
+          <t>דייל</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>סינדני שיר</t>
+          <t>אבריאנוב אירינה</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>05:05</t>
+          <t>05:15</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -4571,8 +4563,16 @@
           <t>06:05</t>
         </is>
       </c>
-      <c r="H90" t="inlineStr"/>
-      <c r="I90" t="inlineStr"/>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>D6</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>שובץ כי העובד מוסמך לתפקיד, פנוי בזמן המשימה וללא חפיפה</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -4597,7 +4597,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>יהל ענבר</t>
+          <t>פרגסליך שחר</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -4617,7 +4617,7 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>שובץ כי העובד מוסמך לתפקיד, פנוי בזמן המשימה וללא חפיפה</t>
+          <t>לא נמצא עובד מתאים: אין זמינות, יש חפיפה או שחסרה הסמכה</t>
         </is>
       </c>
     </row>
@@ -4644,7 +4644,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>עללוש שחר</t>
+          <t>חוזה רון</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -4691,7 +4691,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>רז טל</t>
+          <t>בראל תהילה</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -4738,7 +4738,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>נטע ונטוררו</t>
+          <t>יהל ענבר</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -4785,7 +4785,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>בראל תהילה</t>
+          <t>גלאם שני</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -4832,7 +4832,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>טטרואשוילי טליה</t>
+          <t>ביבי שרון</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -4879,7 +4879,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>סלם חיה</t>
+          <t>ליטמן עידן</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -4926,7 +4926,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>תכלת סגל</t>
+          <t>גנץ עטרה</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -4973,7 +4973,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>בן דב אורנה</t>
+          <t>סוקג'אי ג'סמין</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -5020,7 +5020,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>נטע ונטוררו</t>
+          <t>ונטוררו נטע</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -5067,7 +5067,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>חן אהב</t>
+          <t>פרגסליך שחר</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -5161,7 +5161,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>שרעבי רותם</t>
+          <t>דז'אנשוילי לינוי</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -5208,7 +5208,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>דז'אנשוילי לינוי</t>
+          <t>חן אהב</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -5255,7 +5255,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>טל רז</t>
+          <t>טטרואשוילי טליה</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -5302,7 +5302,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>שחר עללוש</t>
+          <t>אלימלך נועה</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -5349,7 +5349,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>נועה אלימלך</t>
+          <t>אלגבסי ג'ולי</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -5396,7 +5396,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>עידן ליטמן</t>
+          <t>בונטונג מאי</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -5443,7 +5443,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>שורץ נויה</t>
+          <t>סינדני שיר</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -5482,7 +5482,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>מזרחי עדן</t>
+          <t>נועה אלימלך</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -5529,7 +5529,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>שחר פרגסליך</t>
+          <t>חוזה רון</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -5576,7 +5576,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>רמירז אבריל</t>
+          <t>יהל ענבר</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -5623,7 +5623,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>רז טל</t>
+          <t>אבריאנוב אירינה</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -5650,49 +5650,41 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>LY381</t>
+          <t>LY221</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>MXP</t>
+          <t>CDG</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>ראש צוות</t>
+          <t>טרייני ר״צ</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>ראש צוות</t>
+          <t>טרייני רצ</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>אלימלך נועה</t>
+          <t>לילוב רומי</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>06:35</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>07:35</t>
-        </is>
-      </c>
-      <c r="H114" t="inlineStr">
-        <is>
-          <t>E9</t>
-        </is>
-      </c>
-      <c r="I114" t="inlineStr">
-        <is>
-          <t>שובץ כי העובד מוסמך לתפקיד, פנוי בזמן המשימה וללא חפיפה</t>
-        </is>
-      </c>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr"/>
+      <c r="I114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -5707,22 +5699,22 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>דייל 1</t>
+          <t>ראש צוות</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>דייל</t>
+          <t>ראש צוות</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>נטע ונטוררו</t>
+          <t>עללוש שחר</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>06:45</t>
+          <t>06:35</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
@@ -5754,7 +5746,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>דייל 2</t>
+          <t>דייל 1</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -5764,7 +5756,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>ליטמן עידן</t>
+          <t>ונטוררו נטע</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -5801,22 +5793,22 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>טרייני ר״צ</t>
+          <t>דייל 2</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>טרייני רצ</t>
+          <t>דייל</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>שיר סינדני</t>
+          <t>פרגסליך שחר</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>06:35</t>
+          <t>06:45</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
@@ -5824,55 +5816,55 @@
           <t>07:35</t>
         </is>
       </c>
-      <c r="H117" t="inlineStr"/>
-      <c r="I117" t="inlineStr"/>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>E9</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>שובץ כי העובד מוסמך לתפקיד, פנוי בזמן המשימה וללא חפיפה</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>LY347</t>
+          <t>LY381</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>ZRH</t>
+          <t>MXP</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>ראש צוות</t>
+          <t>טרייני ר״צ</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>ראש צוות</t>
+          <t>טרייני רצ</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>שהרבני אוהד</t>
+          <t>שורץ נויה</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>06:35</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="H118" t="inlineStr">
-        <is>
-          <t>E7</t>
-        </is>
-      </c>
-      <c r="I118" t="inlineStr">
-        <is>
-          <t>שובץ כי העובד מוסמך לתפקיד, פנוי בזמן המשימה וללא חפיפה</t>
-        </is>
-      </c>
+          <t>07:35</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr"/>
+      <c r="I118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -5887,22 +5879,22 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>דייל 1</t>
+          <t>ראש צוות</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>דייל</t>
+          <t>ראש צוות</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>נועה אלימלך</t>
+          <t>מזרחי עדן</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
@@ -5934,7 +5926,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>דייל 2</t>
+          <t>דייל 1</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -5944,7 +5936,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>עידן ליטמן</t>
+          <t>אלימלך נועה</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -5971,32 +5963,32 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>LY611</t>
+          <t>LY347</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>DME</t>
+          <t>ZRH</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>ראש צוות</t>
+          <t>דייל 2</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>ראש צוות</t>
+          <t>דייל</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>יהל ענבר</t>
+          <t>סינדני שיר</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>07:10</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
@@ -6006,7 +5998,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>D3</t>
+          <t>E7</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -6028,22 +6020,22 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>דייל</t>
+          <t>ראש צוות</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>דייל</t>
+          <t>ראש צוות</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>שחר עללוש</t>
+          <t>רמירז אבריל</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
@@ -6065,42 +6057,42 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>LY285</t>
+          <t>LY611</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>FCO</t>
+          <t>DME</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>ראש צוות</t>
+          <t>דייל</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>ראש צוות</t>
+          <t>דייל</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>עללוש שחר</t>
+          <t>ליטמן עידן</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>08:05</t>
+          <t>07:10</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>09:05</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>E2</t>
+          <t>D3</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -6122,22 +6114,22 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>דייל 1</t>
+          <t>ראש צוות</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>דייל</t>
+          <t>ראש צוות</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>רז טל</t>
+          <t>יהל ענבר</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>08:05</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
@@ -6169,7 +6161,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>דייל 2</t>
+          <t>דייל 1</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -6179,7 +6171,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>שחר פרגסליך</t>
+          <t>ליטמן עידן</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -6216,22 +6208,22 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>טרייני ר״צ</t>
+          <t>דייל 2</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>טרייני רצ</t>
+          <t>דייל</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>חוזה רון</t>
+          <t>מזרחי עדן</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>08:05</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
@@ -6239,8 +6231,16 @@
           <t>09:05</t>
         </is>
       </c>
-      <c r="H126" t="inlineStr"/>
-      <c r="I126" t="inlineStr"/>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>שובץ כי העובד מוסמך לתפקיד, פנוי בזמן המשימה וללא חפיפה</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -6265,7 +6265,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>ליטמן עידן</t>
+          <t>שהרבני אוהד</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -6312,7 +6312,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>מזרחי עדן</t>
+          <t>נועה אלימלך</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -6359,7 +6359,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>רמירז אבריל</t>
+          <t>עללוש שחר</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -6406,7 +6406,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>שהרבני אוהד</t>
+          <t>אבריאנוב אירינה</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -6453,7 +6453,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>פרילינג דור</t>
+          <t>כהן עדי</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -6480,41 +6480,49 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>LY323</t>
+          <t>LY315</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>CDG</t>
+          <t>LHR</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>טרייני ר״צ</t>
+          <t>ראש צוות</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>טרייני רצ</t>
+          <t>ראש צוות</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>סינדני שיר</t>
+          <t>אלימלך נועה</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>10:00</t>
-        </is>
-      </c>
-      <c r="H132" t="inlineStr"/>
-      <c r="I132" t="inlineStr"/>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>E8</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>שובץ כי העובד מוסמך לתפקיד, פנוי בזמן המשימה וללא חפיפה</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -6529,22 +6537,22 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>ראש צוות</t>
+          <t>דייל 1</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>ראש צוות</t>
+          <t>דייל</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>נועה אלימלך</t>
+          <t>בראל תהילה</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>09:05</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
@@ -6576,7 +6584,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>דייל 1</t>
+          <t>דייל 2</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -6586,7 +6594,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>יהל ענבר</t>
+          <t>גלאם שני</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -6623,7 +6631,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>דייל 2</t>
+          <t>דייל 3</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -6633,7 +6641,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>בראל תהילה</t>
+          <t>גנץ עטרה</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -6670,22 +6678,22 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>דייל 3</t>
+          <t>מתאם תורים</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>דייל</t>
+          <t>מתאם תורים</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>טטרואשוילי טליה</t>
+          <t>דז'אנשוילי לינוי</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>09:05</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
@@ -6717,17 +6725,17 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>מתאם תורים</t>
+          <t>טרייני ר״צ</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>מתאם תורים</t>
+          <t>טרייני רצ</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>תכלת סגל</t>
+          <t>סינדני שיר</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -6740,55 +6748,55 @@
           <t>10:10</t>
         </is>
       </c>
-      <c r="H137" t="inlineStr">
-        <is>
-          <t>E8</t>
-        </is>
-      </c>
-      <c r="I137" t="inlineStr">
-        <is>
-          <t>שובץ כי העובד מוסמך לתפקיד, פנוי בזמן המשימה וללא חפיפה</t>
-        </is>
-      </c>
+      <c r="H137" t="inlineStr"/>
+      <c r="I137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>LY315</t>
+          <t>LY7</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>LHR</t>
+          <t>JFK</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>טרייני ר״צ</t>
+          <t>ראש צוות</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>טרייני רצ</t>
+          <t>ראש צוות</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>שיר סינדני</t>
+          <t>פרגסליך שחר</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>08:55</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>10:10</t>
-        </is>
-      </c>
-      <c r="H138" t="inlineStr"/>
-      <c r="I138" t="inlineStr"/>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>C9</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>שובץ כי העובד מוסמך לתפקיד, פנוי בזמן המשימה וללא חפיפה</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -6803,22 +6811,22 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>ראש צוות</t>
+          <t>דייל 1</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>ראש צוות</t>
+          <t>דייל</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>שחר עללוש</t>
+          <t>חן אהב</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
@@ -6850,7 +6858,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>דייל 1</t>
+          <t>דייל 2</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -6860,7 +6868,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>עללוש שחר</t>
+          <t>טטרואשוילי טליה</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -6897,7 +6905,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>דייל 2</t>
+          <t>דייל 3</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -6907,7 +6915,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>חן אהב</t>
+          <t>ברנע מיכל</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -6944,7 +6952,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>דייל 3</t>
+          <t>דייל 4</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -6954,7 +6962,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>שרעבי רותם</t>
+          <t>כצנלנבוגן רוני</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -6991,22 +6999,22 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>דייל 4</t>
+          <t>מתאם תורים</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>דייל</t>
+          <t>מתאם תורים</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>דז'אנשוילי לינוי</t>
+          <t>מוזס אדיר</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
@@ -7038,12 +7046,12 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>מתאם תורים</t>
+          <t>מפקח TSA</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>מתאם תורים</t>
+          <t>מפקח TSA</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -7053,7 +7061,7 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
@@ -7085,17 +7093,17 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>מפקח TSA</t>
+          <t>שומר TSA</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>מפקח TSA</t>
+          <t>שומר TSA</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>דן קנה</t>
+          <t>טרדווי קלייר</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -7122,42 +7130,42 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>LY7</t>
+          <t>LY5467</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>JFK</t>
+          <t>TIV</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>שומר TSA</t>
+          <t>ראש צוות</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>שומר TSA</t>
+          <t>ראש צוות</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>מוזס אדיר</t>
+          <t>גירו סקיי</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>C9</t>
+          <t>D4</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -7179,22 +7187,22 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>ראש צוות</t>
+          <t>דייל 1</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>ראש צוות</t>
+          <t>דייל</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>גירו סקיי</t>
+          <t>ברנע מיכל</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
@@ -7226,7 +7234,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>דייל 1</t>
+          <t>דייל 2</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -7236,7 +7244,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>חיימובסקי רינה</t>
+          <t>בן דוד עדי</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -7263,42 +7271,42 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>LY5467</t>
+          <t>LY5031</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>TIV</t>
+          <t>RHO</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>דייל 2</t>
+          <t>ראש צוות</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>דייל</t>
+          <t>ראש צוות</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>סוסטיאל מאי</t>
+          <t>גירו סקיי</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>12:10</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>D4</t>
+          <t>C3</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -7320,22 +7328,22 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>ראש צוות</t>
+          <t>דייל</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>ראש צוות</t>
+          <t>דייל</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>גירו סקיי</t>
+          <t>ברנע מיכל</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
@@ -7357,42 +7365,42 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>LY5031</t>
+          <t>LY5431</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>RHO</t>
+          <t>LCA</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>דייל</t>
+          <t>ראש צוות</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>דייל</t>
+          <t>ראש צוות</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>חיימובסקי רינה</t>
+          <t>גדליה מיה</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>C3</t>
+          <t>D3</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -7414,22 +7422,22 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>ראש צוות</t>
+          <t>דייל 1</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>ראש צוות</t>
+          <t>דייל</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>רוזנברג מעיין</t>
+          <t>בן דוד עדי</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
@@ -7461,7 +7469,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>דייל 1</t>
+          <t>דייל 2</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -7471,7 +7479,7 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>סוסטיאל מאי</t>
+          <t>חסון הילה</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
@@ -7508,22 +7516,22 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>דייל 2</t>
+          <t>טרייני ר״צ</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>דייל</t>
+          <t>טרייני רצ</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>בק אהרון</t>
+          <t>אלוני ירדן</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
@@ -7531,55 +7539,55 @@
           <t>13:30</t>
         </is>
       </c>
-      <c r="H154" t="inlineStr">
-        <is>
-          <t>D3</t>
-        </is>
-      </c>
-      <c r="I154" t="inlineStr">
-        <is>
-          <t>שובץ כי העובד מוסמך לתפקיד, פנוי בזמן המשימה וללא חפיפה</t>
-        </is>
-      </c>
+      <c r="H154" t="inlineStr"/>
+      <c r="I154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>LY5431</t>
+          <t>LY5115</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>LCA</t>
+          <t>BUS</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>טרייני ר״צ</t>
+          <t>ראש צוות</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>טרייני רצ</t>
+          <t>ראש צוות</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>אלוני ירדן</t>
+          <t>רוזנברג מעיין</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>13:30</t>
-        </is>
-      </c>
-      <c r="H155" t="inlineStr"/>
-      <c r="I155" t="inlineStr"/>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>E9</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>שובץ כי העובד מוסמך לתפקיד, פנוי בזמן המשימה וללא חפיפה</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -7594,22 +7602,22 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>ראש צוות</t>
+          <t>דייל 1</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>ראש צוות</t>
+          <t>דייל</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>חסון הילה</t>
+          <t>אלבז ניצן</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
@@ -7641,7 +7649,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>דייל 1</t>
+          <t>דייל 2</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -7651,7 +7659,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>דורנשטרוך נעם</t>
+          <t>בלטקסה עומר</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
@@ -7678,42 +7686,42 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>LY5115</t>
+          <t>LY327</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>BUS</t>
+          <t>CDG</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>דייל 2</t>
+          <t>ראש צוות</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>דייל</t>
+          <t>ראש צוות</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>שני פדידה</t>
+          <t>בן דוד נועה</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>E9</t>
+          <t>D5</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -7735,22 +7743,22 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>ראש צוות</t>
+          <t>דייל 1</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>ראש צוות</t>
+          <t>דייל</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>פדידה שני</t>
+          <t>בן נחום מיכל</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
@@ -7782,7 +7790,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>דייל 1</t>
+          <t>דייל 2</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -7792,7 +7800,7 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>בן דוד נועה</t>
+          <t>דורנשטרוך נעם</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
@@ -7829,22 +7837,22 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>דייל 2</t>
+          <t>מתאם תורים</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>דייל</t>
+          <t>מתאם תורים</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>חסיד קורל</t>
+          <t>זוהר יהונתן</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
@@ -7866,42 +7874,42 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>LY327</t>
+          <t>LY613</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>CDG</t>
+          <t>DME</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>מתאם תורים</t>
+          <t>ראש צוות</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>מתאם תורים</t>
+          <t>ראש צוות</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>קהתי נעמה</t>
+          <t>נועה בן דוד</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>D5</t>
+          <t>D6</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
@@ -7923,22 +7931,22 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>ראש צוות</t>
+          <t>דייל 1</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>ראש צוות</t>
+          <t>דייל</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>גדליה מיה</t>
+          <t>זייגר רויטל</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
@@ -7953,7 +7961,7 @@
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>לא נמצא עובד מתאים: אין זמינות, יש חפיפה או שחסרה הסמכה</t>
+          <t>שובץ כי העובד מוסמך לתפקיד, פנוי בזמן המשימה וללא חפיפה</t>
         </is>
       </c>
     </row>
@@ -7970,7 +7978,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>דייל 1</t>
+          <t>דייל 2</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -7980,7 +7988,7 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>אלבז ניצן</t>
+          <t>זערור עידו</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
@@ -8007,27 +8015,27 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>LY613</t>
+          <t>LY5437</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>DME</t>
+          <t>PFO</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>דייל 2</t>
+          <t>ראש צוות</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>דייל</t>
+          <t>ראש צוות</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>מרום נגה</t>
+          <t>פדידה שני</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
@@ -8037,12 +8045,12 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>D6</t>
+          <t>D7</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -8064,22 +8072,22 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>ראש צוות</t>
+          <t>דייל 1</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>ראש צוות</t>
+          <t>דייל</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>נועה בן דוד</t>
+          <t>גירו סקיי</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
@@ -8094,7 +8102,7 @@
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>לא נמצא עובד מתאים: אין זמינות, יש חפיפה או שחסרה הסמכה</t>
+          <t>שובץ כי העובד מוסמך לתפקיד, פנוי בזמן המשימה וללא חפיפה</t>
         </is>
       </c>
     </row>
@@ -8111,7 +8119,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>דייל 1</t>
+          <t>דייל 2</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -8121,7 +8129,7 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>גירו סקיי</t>
+          <t>ברנע מיכל</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
@@ -8158,7 +8166,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>דייל 2</t>
+          <t>דייל 3</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -8168,7 +8176,7 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>חיימובסקי רינה</t>
+          <t>חסיד קורל</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
@@ -8195,42 +8203,42 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>LY5437</t>
+          <t>LY281</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>PFO</t>
+          <t>MXP</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>דייל 3</t>
+          <t>ראש צוות</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>דייל</t>
+          <t>ראש צוות</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>נח גל</t>
+          <t>חסון הילה</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>D7</t>
+          <t>C8</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
@@ -8252,22 +8260,22 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>ראש צוות</t>
+          <t>דייל 1</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>ראש צוות</t>
+          <t>דייל</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>נועה בן דוד</t>
+          <t>גירו סקיי</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
@@ -8299,7 +8307,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>דייל 1</t>
+          <t>דייל 2</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -8309,7 +8317,7 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>גירו סקיי</t>
+          <t>בן דוד עדי</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
@@ -8336,42 +8344,42 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>LY281</t>
+          <t>LY351</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>MXP</t>
+          <t>MUC</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>דייל 2</t>
+          <t>ראש צוות</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>דייל</t>
+          <t>ראש צוות</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>חיימובסקי רינה</t>
+          <t>גדליה מיה</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>C8</t>
+          <t>E8</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
@@ -8383,41 +8391,49 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>LY281</t>
+          <t>LY351</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>MXP</t>
+          <t>MUC</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>טרייני ר״צ</t>
+          <t>דייל 1</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>טרייני רצ</t>
+          <t>דייל</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>אלוני ירדן</t>
+          <t>רוזנברג מעיין</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>15:30</t>
-        </is>
-      </c>
-      <c r="H173" t="inlineStr"/>
-      <c r="I173" t="inlineStr"/>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>E8</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>שובץ כי העובד מוסמך לתפקיד, פנוי בזמן המשימה וללא חפיפה</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -8432,22 +8448,22 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>ראש צוות</t>
+          <t>דייל 2</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>ראש צוות</t>
+          <t>דייל</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>שני פדידה</t>
+          <t>אלבז ניצן</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
@@ -8479,22 +8495,22 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>דייל 1</t>
+          <t>טרייני ר״צ</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>דייל</t>
+          <t>טרייני רצ</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>סוסטיאל מאי</t>
+          <t>אלוני ירדן</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
@@ -8502,56 +8518,48 @@
           <t>15:45</t>
         </is>
       </c>
-      <c r="H175" t="inlineStr">
-        <is>
-          <t>E8</t>
-        </is>
-      </c>
-      <c r="I175" t="inlineStr">
-        <is>
-          <t>שובץ כי העובד מוסמך לתפקיד, פנוי בזמן המשימה וללא חפיפה</t>
-        </is>
-      </c>
+      <c r="H175" t="inlineStr"/>
+      <c r="I175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>LY351</t>
+          <t>LY313</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>MUC</t>
+          <t>LTN</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>דייל 2</t>
+          <t>ראש צוות</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>דייל</t>
+          <t>ראש צוות</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>רוזנברג מעיין</t>
+          <t>בן דוד נועה</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>E8</t>
+          <t>D4</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
@@ -8573,22 +8581,22 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>ראש צוות</t>
+          <t>דייל 1</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>ראש צוות</t>
+          <t>דייל</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>גדליה מיה</t>
+          <t>בלטקסה עומר</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
@@ -8620,7 +8628,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>דייל 1</t>
+          <t>דייל 2</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -8630,7 +8638,7 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>פדידה שני</t>
+          <t>בן נחום מיכל</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
@@ -8657,32 +8665,32 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>LY313</t>
+          <t>LY339</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>LTN</t>
+          <t>AMS</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>דייל 2</t>
+          <t>ראש צוות</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>דייל</t>
+          <t>ראש צוות</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>בן דוד נועה</t>
+          <t>נועה בן דוד</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
@@ -8692,7 +8700,7 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>D4</t>
+          <t>D5</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
@@ -8714,22 +8722,22 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>ראש צוות</t>
+          <t>דייל 1</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>ראש צוות</t>
+          <t>דייל</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>חסון הילה</t>
+          <t>דורנשטרוך נעם</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
@@ -8761,7 +8769,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>דייל 1</t>
+          <t>דייל 2</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -8771,7 +8779,7 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>חסיד קורל</t>
+          <t>זוהר יהונתן</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
@@ -8798,42 +8806,42 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>LY339</t>
+          <t>LY5141</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>AMS</t>
+          <t>LCA</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>דייל 2</t>
+          <t>ראש צוות</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>דייל</t>
+          <t>ראש צוות</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>קהתי נעמה</t>
+          <t>פדידה שני</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>D5</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
@@ -8855,22 +8863,22 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>ראש צוות</t>
+          <t>דייל</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>ראש צוות</t>
+          <t>דייל</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>הלמן עמית</t>
+          <t>זייגר רויטל</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
@@ -8892,42 +8900,42 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>LY5141</t>
+          <t>LY343</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>LCA</t>
+          <t>ZRH</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>דייל</t>
+          <t>ראש צוות</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>דייל</t>
+          <t>ראש צוות</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>אלבז ניצן</t>
+          <t>חסון הילה</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>C2</t>
+          <t>E2</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
@@ -8949,22 +8957,22 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>ראש צוות</t>
+          <t>דייל 1</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>ראש צוות</t>
+          <t>דייל</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>נועה בן דוד</t>
+          <t>בן דוד עדי</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
@@ -8996,7 +9004,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>דייל 1</t>
+          <t>דייל 2</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -9006,7 +9014,7 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>מרום נגה</t>
+          <t>זערור עידו</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
@@ -9033,42 +9041,42 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>LY343</t>
+          <t>LY375</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>ZRH</t>
+          <t>LIS</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>דייל 2</t>
+          <t>ראש צוות</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>דייל</t>
+          <t>ראש צוות</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>נח גל</t>
+          <t>רוזנברג מעיין</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>E2</t>
+          <t>D3</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
@@ -9080,41 +9088,49 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>LY343</t>
+          <t>LY375</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>ZRH</t>
+          <t>LIS</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>טרייני ר״צ</t>
+          <t>דייל 1</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>טרייני רצ</t>
+          <t>דייל</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>אלוני ירדן</t>
+          <t>גדליה מיה</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>16:35</t>
-        </is>
-      </c>
-      <c r="H188" t="inlineStr"/>
-      <c r="I188" t="inlineStr"/>
+          <t>16:55</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>D3</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>שובץ כי העובד מוסמך לתפקיד, פנוי בזמן המשימה וללא חפיפה</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -9129,22 +9145,22 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>ראש צוות</t>
+          <t>דייל 2</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>ראש צוות</t>
+          <t>דייל</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>שני פדידה</t>
+          <t>אלבז ניצן</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
@@ -9176,22 +9192,22 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>דייל 1</t>
+          <t>טרייני ר״צ</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>דייל</t>
+          <t>טרייני רצ</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>חיימובסקי רינה</t>
+          <t>אלוני ירדן</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
@@ -9199,56 +9215,48 @@
           <t>16:55</t>
         </is>
       </c>
-      <c r="H190" t="inlineStr">
-        <is>
-          <t>D3</t>
-        </is>
-      </c>
-      <c r="I190" t="inlineStr">
-        <is>
-          <t>שובץ כי העובד מוסמך לתפקיד, פנוי בזמן המשימה וללא חפיפה</t>
-        </is>
-      </c>
+      <c r="H190" t="inlineStr"/>
+      <c r="I190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>LY375</t>
+          <t>LY223</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>LIS</t>
+          <t>NCE</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>דייל 2</t>
+          <t>ראש צוות</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>דייל</t>
+          <t>ראש צוות</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>סוסטיאל מאי</t>
+          <t>פליק נועה</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>D3</t>
+          <t>C6</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
@@ -9270,22 +9278,22 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>ראש צוות</t>
+          <t>דייל</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>ראש צוות</t>
+          <t>דייל</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>פליק נועה</t>
+          <t>חסיד קורל</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
@@ -9307,32 +9315,32 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>LY223</t>
+          <t>LY317</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>NCE</t>
+          <t>LHR</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>דייל</t>
+          <t>ראש צוות</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>דייל</t>
+          <t>ראש צוות</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>זוארץ שיראל</t>
+          <t>הלמן עמית</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
@@ -9342,7 +9350,7 @@
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>C6</t>
+          <t>D9</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
@@ -9364,22 +9372,22 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>ראש צוות</t>
+          <t>דייל 1</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>ראש צוות</t>
+          <t>דייל</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>גירו סקיי</t>
+          <t>לשם גבי</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
@@ -9411,7 +9419,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>דייל 1</t>
+          <t>דייל 2</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -9421,7 +9429,7 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>חן הדר</t>
+          <t>דולד הדר</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
@@ -9458,7 +9466,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>דייל 2</t>
+          <t>דייל 3</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -9468,7 +9476,7 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>סעדיה שחף</t>
+          <t>ורנר אליאן</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
@@ -9505,22 +9513,22 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>דייל 3</t>
+          <t>מתאם תורים</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>דייל</t>
+          <t>מתאם תורים</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>דולד הדר</t>
+          <t>זוארץ שיראל</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
@@ -9542,42 +9550,42 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>LY317</t>
+          <t>LY397</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>LHR</t>
+          <t>MAD</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>מתאם תורים</t>
+          <t>ראש צוות</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>מתאם תורים</t>
+          <t>ראש צוות</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>ורנר אליאן</t>
+          <t>בן דוד נועה</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>D9</t>
+          <t>E3</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
@@ -9599,22 +9607,22 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>ראש צוות</t>
+          <t>דייל 1</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>ראש צוות</t>
+          <t>דייל</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>בן דוד נועה</t>
+          <t>בלטקסה עומר</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
@@ -9646,7 +9654,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>דייל 1</t>
+          <t>דייל 2</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -9656,7 +9664,7 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>בק אהרון</t>
+          <t>בן נחום מיכל</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
@@ -9683,32 +9691,32 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>LY397</t>
+          <t>LY545</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>MAD</t>
+          <t>ATH</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>דייל 2</t>
+          <t>ראש צוות</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>דייל</t>
+          <t>ראש צוות</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>דורנשטרוך נעם</t>
+          <t>נועה בן דוד</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
@@ -9718,7 +9726,7 @@
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>E3</t>
+          <t>D6</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
@@ -9740,22 +9748,22 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>ראש צוות</t>
+          <t>דייל 1</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>ראש צוות</t>
+          <t>דייל</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>חסון הילה</t>
+          <t>דורנשטרוך נעם</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
@@ -9787,7 +9795,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>דייל 1</t>
+          <t>דייל 2</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -9797,7 +9805,7 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>חסיד קורל</t>
+          <t>זוהר יהונתן</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
@@ -9824,42 +9832,42 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>LY545</t>
+          <t>LY363</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>ATH</t>
+          <t>VIE</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>דייל 2</t>
+          <t>ראש צוות</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>דייל</t>
+          <t>ראש צוות</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>קהתי נעמה</t>
+          <t>פדידה שני</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>16:25</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>D6</t>
+          <t>D2</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
@@ -9881,22 +9889,22 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>ראש צוות</t>
+          <t>דייל 1</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>ראש צוות</t>
+          <t>דייל</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>הלמן עמית</t>
+          <t>בן דוד עדי</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
@@ -9928,7 +9936,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>דייל 1</t>
+          <t>דייל 2</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -9938,7 +9946,7 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>נועה בן דוד</t>
+          <t>זייגר רויטל</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
@@ -9965,42 +9973,42 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>LY363</t>
+          <t>LY391</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>VIE</t>
+          <t>BCN</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>דייל 2</t>
+          <t>ראש צוות</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>דייל</t>
+          <t>ראש צוות</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>אלבז ניצן</t>
+          <t>גירו סקיי</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>D2</t>
+          <t>C8</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
@@ -10022,22 +10030,22 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>ראש צוות</t>
+          <t>דייל</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>ראש צוות</t>
+          <t>דייל</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>רוזנברג מעיין</t>
+          <t>זערור עידו</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
@@ -10052,7 +10060,7 @@
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t>לא נמצא עובד מתאים: אין זמינות, יש חפיפה או שחסרה הסמכה</t>
+          <t>שובץ כי העובד מוסמך לתפקיד, פנוי בזמן המשימה וללא חפיפה</t>
         </is>
       </c>
     </row>
@@ -10069,22 +10077,22 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>דייל</t>
+          <t>מתאם תורים</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>דייל</t>
+          <t>מתאם תורים</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>מרום נגה</t>
+          <t>חן הדר</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
@@ -10106,47 +10114,47 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>LY391</t>
+          <t>LY2523</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>BCN</t>
+          <t>PRG</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>מתאם תורים</t>
+          <t>ראש צוות</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>מתאם תורים</t>
+          <t>ראש צוות</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>נח גל</t>
+          <t>חסון הילה</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>C8</t>
+          <t>E8</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t>שובץ כי העובד מוסמך לתפקיד, פנוי בזמן המשימה וללא חפיפה</t>
+          <t>לא נמצא עובד מתאים: אין זמינות, יש חפיפה או שחסרה הסמכה</t>
         </is>
       </c>
     </row>
@@ -10163,22 +10171,22 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>ראש צוות</t>
+          <t>דייל</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>ראש צוות</t>
+          <t>דייל</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>גדליה מיה</t>
+          <t>פליק נועה</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
@@ -10193,49 +10201,49 @@
       </c>
       <c r="I211" t="inlineStr">
         <is>
-          <t>לא נמצא עובד מתאים: אין זמינות, יש חפיפה או שחסרה הסמכה</t>
+          <t>שובץ כי העובד מוסמך לתפקיד, פנוי בזמן המשימה וללא חפיפה</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>LY2523</t>
+          <t>LY383</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>PRG</t>
+          <t>FCO</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>דייל</t>
+          <t>ראש צוות</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>דייל</t>
+          <t>ראש צוות</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>שני פדידה</t>
+          <t>רוזנברג מעיין</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>E8</t>
+          <t>C3</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
@@ -10257,22 +10265,22 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>ראש צוות</t>
+          <t>דייל 1</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>ראש צוות</t>
+          <t>דייל</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>רוזנברג מעיין</t>
+          <t>חסיד קורל</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
@@ -10304,7 +10312,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>דייל 1</t>
+          <t>דייל 2</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -10314,7 +10322,7 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>פליק נועה</t>
+          <t>אלבז ניצן</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
@@ -10351,22 +10359,22 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>דייל 2</t>
+          <t>טרייני ר״צ</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>דייל</t>
+          <t>טרייני רצ</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>זוארץ שיראל</t>
+          <t>אלוני ירדן</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
@@ -10374,41 +10382,33 @@
           <t>18:00</t>
         </is>
       </c>
-      <c r="H215" t="inlineStr">
-        <is>
-          <t>C3</t>
-        </is>
-      </c>
-      <c r="I215" t="inlineStr">
-        <is>
-          <t>שובץ כי העובד מוסמך לתפקיד, פנוי בזמן המשימה וללא חפיפה</t>
-        </is>
-      </c>
+      <c r="H215" t="inlineStr"/>
+      <c r="I215" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>LY383</t>
+          <t>LY289</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>FCO</t>
+          <t>VCE</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>טרייני ר״צ</t>
+          <t>ראש צוות</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>טרייני רצ</t>
+          <t>ראש צוות</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>אלוני ירדן</t>
+          <t>גדליה מיה</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
@@ -10421,8 +10421,16 @@
           <t>18:00</t>
         </is>
       </c>
-      <c r="H216" t="inlineStr"/>
-      <c r="I216" t="inlineStr"/>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>E4</t>
+        </is>
+      </c>
+      <c r="I216" t="inlineStr">
+        <is>
+          <t>לא נמצא עובד מתאים: אין זמינות, יש חפיפה או שחסרה הסמכה</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -10437,22 +10445,22 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>ראש צוות</t>
+          <t>דייל</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>ראש צוות</t>
+          <t>דייל</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>פדידה שני</t>
+          <t>הלמן עמית</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>17:10</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
@@ -10467,49 +10475,49 @@
       </c>
       <c r="I217" t="inlineStr">
         <is>
-          <t>לא נמצא עובד מתאים: אין זמינות, יש חפיפה או שחסרה הסמכה</t>
+          <t>שובץ כי העובד מוסמך לתפקיד, פנוי בזמן המשימה וללא חפיפה</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>LY289</t>
+          <t>LY387</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>VCE</t>
+          <t>MXP</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>דייל</t>
+          <t>ראש צוות</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>דייל</t>
+          <t>ראש צוות</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>חן הדר</t>
+          <t>בן דוד נועה</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>17:10</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>E4</t>
+          <t>D5</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
@@ -10531,22 +10539,22 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>ראש צוות</t>
+          <t>דייל 1</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>ראש צוות</t>
+          <t>דייל</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>גדליה מיה</t>
+          <t>בלטקסה עומר</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
@@ -10578,7 +10586,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>דייל 1</t>
+          <t>דייל 2</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -10588,7 +10596,7 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>פדידה שני</t>
+          <t>בן נחום מיכל</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
@@ -10615,32 +10623,32 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>LY387</t>
+          <t>LY571</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>MXP</t>
+          <t>OTP</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>דייל 2</t>
+          <t>ראש צוות</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>דייל</t>
+          <t>ראש צוות</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>בן דוד נועה</t>
+          <t>נועה בן דוד</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
@@ -10650,7 +10658,7 @@
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>D5</t>
+          <t>E9</t>
         </is>
       </c>
       <c r="I221" t="inlineStr">
@@ -10672,22 +10680,22 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>ראש צוות</t>
+          <t>דייל 1</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>ראש צוות</t>
+          <t>דייל</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>חסון הילה</t>
+          <t>דורנשטרוך נעם</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
@@ -10719,7 +10727,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>דייל 1</t>
+          <t>דייל 2</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -10729,7 +10737,7 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>הלמן עמית</t>
+          <t>זוהר יהונתן</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
@@ -10756,42 +10764,42 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>LY571</t>
+          <t>LY5183</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>OTP</t>
+          <t>TIA</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>דייל 2</t>
+          <t>ראש צוות</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>דייל</t>
+          <t>ראש צוות</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>חסיד קורל</t>
+          <t>הלמן עמית</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>E9</t>
+          <t>E2</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
@@ -10813,22 +10821,22 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>ראש צוות</t>
+          <t>דייל 1</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>ראש צוות</t>
+          <t>דייל</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>פליק נועה</t>
+          <t>זייגר רויטל</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
@@ -10860,7 +10868,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>דייל 1</t>
+          <t>דייל 2</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -10870,7 +10878,7 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>קהתי נעמה</t>
+          <t>זערור עידו</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
@@ -10907,22 +10915,22 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>דייל 2</t>
+          <t>טרייני ר״צ</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>דייל</t>
+          <t>טרייני רצ</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>אלבז ניצן</t>
+          <t>לילייב יבה</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
@@ -10930,16 +10938,8 @@
           <t>19:10</t>
         </is>
       </c>
-      <c r="H227" t="inlineStr">
-        <is>
-          <t>E2</t>
-        </is>
-      </c>
-      <c r="I227" t="inlineStr">
-        <is>
-          <t>שובץ כי העובד מוסמך לתפקיד, פנוי בזמן המשימה וללא חפיפה</t>
-        </is>
-      </c>
+      <c r="H227" t="inlineStr"/>
+      <c r="I227" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -10964,7 +10964,7 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>ויינברג ליזי</t>
+          <t>פליק נועה</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
@@ -11011,7 +11011,7 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>מרום נגה</t>
+          <t>חסיד קורל</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
@@ -11058,7 +11058,7 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>נח גל</t>
+          <t>לשם גבי</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
@@ -11105,7 +11105,7 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>זוארץ שיראל</t>
+          <t>דולד הדר</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
@@ -11152,7 +11152,7 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>סעדיה שחף</t>
+          <t>ורנר אליאן</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
@@ -11199,7 +11199,7 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>צוויקל נועה</t>
+          <t>ויינברג ליזי</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
@@ -11246,7 +11246,7 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>הלמן עמית</t>
+          <t>זוארץ שיראל</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
@@ -11340,7 +11340,7 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>אבו רומאנה אליאן</t>
+          <t>צוויקל נועה</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
@@ -11387,7 +11387,7 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>דולד הדר</t>
+          <t>אבו רומאנה אליאן</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
@@ -11414,41 +11414,49 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>LY543</t>
+          <t>LY2367</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>ATH</t>
+          <t>BUD</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>טרייני ר״צ</t>
+          <t>ראש צוות</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>טרייני רצ</t>
+          <t>ראש צוות</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>לילייב יבה</t>
+          <t>גדליה מיה</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>19:30</t>
-        </is>
-      </c>
-      <c r="H238" t="inlineStr"/>
-      <c r="I238" t="inlineStr"/>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="H238" t="inlineStr">
+        <is>
+          <t>D6</t>
+        </is>
+      </c>
+      <c r="I238" t="inlineStr">
+        <is>
+          <t>שובץ כי העובד מוסמך לתפקיד, פנוי בזמן המשימה וללא חפיפה</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -11463,22 +11471,22 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>ראש צוות</t>
+          <t>דייל 1</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>ראש צוות</t>
+          <t>דייל</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>פדידה שני</t>
+          <t>מנצור חנה</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
@@ -11510,7 +11518,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>דייל 1</t>
+          <t>דייל 2</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -11520,7 +11528,7 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>ורנר אליאן</t>
+          <t>דמארי נועה</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
@@ -11557,22 +11565,22 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>דייל 2</t>
+          <t>טרייני ר״צ</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>דייל</t>
+          <t>טרייני רצ</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>אוחנה חן</t>
+          <t>אלוני ירדן</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
@@ -11580,16 +11588,8 @@
           <t>19:40</t>
         </is>
       </c>
-      <c r="H241" t="inlineStr">
-        <is>
-          <t>D6</t>
-        </is>
-      </c>
-      <c r="I241" t="inlineStr">
-        <is>
-          <t>שובץ כי העובד מוסמך לתפקיד, פנוי בזמן המשימה וללא חפיפה</t>
-        </is>
-      </c>
+      <c r="H241" t="inlineStr"/>
+      <c r="I241" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -11614,7 +11614,7 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>נועה בן דוד</t>
+          <t>חסון הילה</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
@@ -11661,7 +11661,7 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>שיילו בר</t>
+          <t>פידלמן נירית</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
@@ -11708,7 +11708,7 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>פידלמן נירית</t>
+          <t>בר שיילו</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
@@ -11755,7 +11755,7 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>דמארי נועה</t>
+          <t>אוחנה חן</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
@@ -11782,41 +11782,49 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>LY5137</t>
+          <t>LY91</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>PFO</t>
+          <t>NRT</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>טרייני ר״צ</t>
+          <t>ראש צוות</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>טרייני רצ</t>
+          <t>ראש צוות</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>אלוני ירדן</t>
+          <t>רוזנברג מעיין</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>19:40</t>
-        </is>
-      </c>
-      <c r="H246" t="inlineStr"/>
-      <c r="I246" t="inlineStr"/>
+          <t>19:45</t>
+        </is>
+      </c>
+      <c r="H246" t="inlineStr">
+        <is>
+          <t>D9</t>
+        </is>
+      </c>
+      <c r="I246" t="inlineStr">
+        <is>
+          <t>שובץ כי העובד מוסמך לתפקיד, פנוי בזמן המשימה וללא חפיפה</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -11831,22 +11839,22 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>ראש צוות</t>
+          <t>דייל 1</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>ראש צוות</t>
+          <t>דייל</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>שני פדידה</t>
+          <t>יעקב ים</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
@@ -11878,7 +11886,7 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>דייל 1</t>
+          <t>דייל 2</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -11888,7 +11896,7 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>יעקב ים</t>
+          <t>מורד לינוי</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
@@ -11925,7 +11933,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>דייל 2</t>
+          <t>דייל 3</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -11935,7 +11943,7 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>מורד לינוי</t>
+          <t>סעדיה שחף</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
@@ -11962,42 +11970,42 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>LY91</t>
+          <t>LY11</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>NRT</t>
+          <t>JFK</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>דייל 3</t>
+          <t>ראש צוות</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>דייל</t>
+          <t>ראש צוות</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>רוב נועה</t>
+          <t>פליק נועה</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>19:45</t>
+          <t>20:45</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>D9</t>
+          <t>E6</t>
         </is>
       </c>
       <c r="I250" t="inlineStr">
@@ -12019,22 +12027,22 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>ראש צוות</t>
+          <t>דייל 1</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>ראש צוות</t>
+          <t>דייל</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>ויינברג ליזי</t>
+          <t>לשם גבי</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
@@ -12066,7 +12074,7 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>דייל 1</t>
+          <t>דייל 2</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -12076,7 +12084,7 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>פליק נועה</t>
+          <t>דולד הדר</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
@@ -12113,7 +12121,7 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>דייל 2</t>
+          <t>דייל 3</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
@@ -12123,7 +12131,7 @@
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>זוארץ שיראל</t>
+          <t>ורנר אליאן</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
@@ -12160,7 +12168,7 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>דייל 3</t>
+          <t>דייל 4</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -12170,7 +12178,7 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>חן הדר</t>
+          <t>זוארץ שיראל</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
@@ -12207,22 +12215,22 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>דייל 4</t>
+          <t>מתאם תורים</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>דייל</t>
+          <t>מתאם תורים</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>סעדיה שחף</t>
+          <t>לילייב יבה</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
@@ -12254,22 +12262,22 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>מתאם תורים</t>
+          <t>מפקח TSA</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>מתאם תורים</t>
+          <t>מפקח TSA</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>אברהם ירדן</t>
+          <t>בק אהרון</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>18:45</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
@@ -12301,17 +12309,17 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>מפקח TSA</t>
+          <t>שומר TSA</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>מפקח TSA</t>
+          <t>שומר TSA</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>בק אהרון</t>
+          <t>רוב נועה</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
@@ -12338,42 +12346,42 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>LY11</t>
+          <t>LY5109</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>JFK</t>
+          <t>TBS</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>שומר TSA</t>
+          <t>ראש צוות</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>שומר TSA</t>
+          <t>ראש צוות</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>דורנשטרוך נעם</t>
+          <t>אבו רומאנה אליאן</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>18:45</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>20:45</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>E6</t>
+          <t>E3</t>
         </is>
       </c>
       <c r="I258" t="inlineStr">
@@ -12395,22 +12403,22 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>ראש צוות</t>
+          <t>דייל 1</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>ראש צוות</t>
+          <t>דייל</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>צוויקל נועה</t>
+          <t>חסיד קורל</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>19:50</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
@@ -12442,7 +12450,7 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>דייל 1</t>
+          <t>דייל 2</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -12452,7 +12460,7 @@
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>דולד הדר</t>
+          <t>חן הדר</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
@@ -12489,22 +12497,22 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>דייל 2</t>
+          <t>טרייני ר״צ</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>דייל</t>
+          <t>טרייני רצ</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>ורנר אליאן</t>
+          <t>אלוני ירדן</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
@@ -12512,16 +12520,8 @@
           <t>20:50</t>
         </is>
       </c>
-      <c r="H261" t="inlineStr">
-        <is>
-          <t>E3</t>
-        </is>
-      </c>
-      <c r="I261" t="inlineStr">
-        <is>
-          <t>שובץ כי העובד מוסמך לתפקיד, פנוי בזמן המשימה וללא חפיפה</t>
-        </is>
-      </c>
+      <c r="H261" t="inlineStr"/>
+      <c r="I261" t="inlineStr"/>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -12546,7 +12546,7 @@
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>אבו רומאנה אליאן</t>
+          <t>ויינברג ליזי</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
@@ -12593,7 +12593,7 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>אוחנה חן</t>
+          <t>צוויקל נועה</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
@@ -12620,41 +12620,49 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>LY5133</t>
+          <t>LY5129</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>LCA</t>
+          <t>RMO</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>טרייני ר״צ</t>
+          <t>ראש צוות</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>טרייני רצ</t>
+          <t>ראש צוות</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>לילייב יבה</t>
+          <t>הלמן עמית</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>19:50</t>
+          <t>20:15</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>20:50</t>
-        </is>
-      </c>
-      <c r="H264" t="inlineStr"/>
-      <c r="I264" t="inlineStr"/>
+          <t>21:15</t>
+        </is>
+      </c>
+      <c r="H264" t="inlineStr">
+        <is>
+          <t>D5</t>
+        </is>
+      </c>
+      <c r="I264" t="inlineStr">
+        <is>
+          <t>לא נמצא עובד מתאים: אין זמינות, יש חפיפה או שחסרה הסמכה</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -12669,22 +12677,22 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>ראש צוות</t>
+          <t>דייל 1</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>ראש צוות</t>
+          <t>דייל</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>הלמן עמית</t>
+          <t>מנצור חנה</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>20:15</t>
+          <t>20:25</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
@@ -12716,7 +12724,7 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>דייל 1</t>
+          <t>דייל 2</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
@@ -12726,7 +12734,7 @@
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>שיילו בר</t>
+          <t>דמארי נועה</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
@@ -12745,53 +12753,6 @@
         </is>
       </c>
       <c r="I266" t="inlineStr">
-        <is>
-          <t>שובץ כי העובד מוסמך לתפקיד, פנוי בזמן המשימה וללא חפיפה</t>
-        </is>
-      </c>
-    </row>
-    <row r="267">
-      <c r="A267" t="inlineStr">
-        <is>
-          <t>LY5129</t>
-        </is>
-      </c>
-      <c r="B267" t="inlineStr">
-        <is>
-          <t>RMO</t>
-        </is>
-      </c>
-      <c r="C267" t="inlineStr">
-        <is>
-          <t>דייל 2</t>
-        </is>
-      </c>
-      <c r="D267" t="inlineStr">
-        <is>
-          <t>דייל</t>
-        </is>
-      </c>
-      <c r="E267" t="inlineStr">
-        <is>
-          <t>פידלמן נירית</t>
-        </is>
-      </c>
-      <c r="F267" t="inlineStr">
-        <is>
-          <t>20:25</t>
-        </is>
-      </c>
-      <c r="G267" t="inlineStr">
-        <is>
-          <t>21:15</t>
-        </is>
-      </c>
-      <c r="H267" t="inlineStr">
-        <is>
-          <t>D5</t>
-        </is>
-      </c>
-      <c r="I267" t="inlineStr">
         <is>
           <t>שובץ כי העובד מוסמך לתפקיד, פנוי בזמן המשימה וללא חפיפה</t>
         </is>
